--- a/nuevo proyecto.xlsx
+++ b/nuevo proyecto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autopartesymas-my.sharepoint.com/personal/luis_torres_apymsa_com_mx/Documents/Escritorio/APP JOSE LUIS/APP ANDROIDS/Nueva carpeta (4)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7696404F-F840-4AA0-A133-AC07F0CA0F88}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFBCBD31-C924-40A9-8F0F-E4CF494D8E22}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{75B1F3C8-71D0-457A-B54E-A3BBFEA49E49}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{75B1F3C8-71D0-457A-B54E-A3BBFEA49E49}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="226">
   <si>
     <t>Marca</t>
   </si>
@@ -702,6 +702,12 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7f5f183f5d176a341e21ee5fa37f8ee7ad31176a/DIFUS-T4.png</t>
+  </si>
+  <si>
+    <t>SERGIO PELGO ARREDONDO</t>
+  </si>
+  <si>
+    <t>EJ.COMPUERTAS</t>
   </si>
 </sst>
 </file>
@@ -2885,7 +2891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA9993D9-3B33-4EBB-A2AC-946678745516}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.36328125" style="2" bestFit="1" customWidth="1"/>
@@ -2937,6 +2943,26 @@
         <v>11</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>9998</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" s="2">
+        <v>6681620106</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F2" xr:uid="{EA9993D9-3B33-4EBB-A2AC-946678745516}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/nuevo proyecto.xlsx
+++ b/nuevo proyecto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autopartesymas-my.sharepoint.com/personal/luis_torres_apymsa_com_mx/Documents/Escritorio/APP JOSE LUIS/APP ANDROIDS/Nueva carpeta (4)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFBCBD31-C924-40A9-8F0F-E4CF494D8E22}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E51A106B-33A9-4210-90C9-68AF46D9D484}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{75B1F3C8-71D0-457A-B54E-A3BBFEA49E49}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{75B1F3C8-71D0-457A-B54E-A3BBFEA49E49}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="237">
   <si>
     <t>Marca</t>
   </si>
@@ -708,6 +708,39 @@
   </si>
   <si>
     <t>EJ.COMPUERTAS</t>
+  </si>
+  <si>
+    <t>001457500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELEVADOR UNIVERSAL 24V 30A-40A WEISCHLER </t>
+  </si>
+  <si>
+    <t>WEISCHLER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELEVADOR UNIVERSAL 12V 20A-30A FORD CHRYSLER CHEVROLET JEEP BOSCH </t>
+  </si>
+  <si>
+    <t>BOSCH</t>
+  </si>
+  <si>
+    <t>001458006</t>
+  </si>
+  <si>
+    <t>001458000</t>
+  </si>
+  <si>
+    <t>RELEVADOR UNIVERSAL 12V 20A-30A FORD CHRYSLER CHEVROLET JEEP WEISCHLER</t>
+  </si>
+  <si>
+    <t>https://resources.apymsa.com.mx/imagenes/FotosSpeed/1458000/14580003a.jpg</t>
+  </si>
+  <si>
+    <t>https://resources.apymsa.com.mx/imagenes/FotosSpeed/1458006/14580063a.jpg</t>
+  </si>
+  <si>
+    <t>https://resources.apymsa.com.mx/imagenes/FotosSpeed/1457500/14575003a.jpg</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE22E9D8-5D11-4958-B13F-1AFF91466E25}">
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="1"/>
@@ -2882,10 +2915,74 @@
         <v>1</v>
       </c>
     </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D105" s="1">
+        <v>75</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D106" s="1">
+        <v>60</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D107" s="1">
+        <v>50</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="str">
+        <f>TEXT(A106,"000000000")</f>
+        <v>001458006</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="str">
+        <f>TEXT(A107,"000000000")</f>
+        <v>001458000</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E104" xr:uid="{EE22E9D8-5D11-4958-B13F-1AFF91466E25}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2967,5 +3064,6 @@
   <autoFilter ref="A1:F2" xr:uid="{EA9993D9-3B33-4EBB-A2AC-946678745516}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/nuevo proyecto.xlsx
+++ b/nuevo proyecto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autopartesymas-my.sharepoint.com/personal/luis_torres_apymsa_com_mx/Documents/Escritorio/APP JOSE LUIS/APP ANDROIDS/Nueva carpeta (4)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E51A106B-33A9-4210-90C9-68AF46D9D484}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F13016D7-1A43-4A0E-AB9E-3C3BE493EEAF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{75B1F3C8-71D0-457A-B54E-A3BBFEA49E49}"/>
   </bookViews>
@@ -1138,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE22E9D8-5D11-4958-B13F-1AFF91466E25}">
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="1"/>
@@ -2964,18 +2964,6 @@
       </c>
       <c r="E107" s="1" t="s">
         <v>234</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A108" s="1" t="str">
-        <f>TEXT(A106,"000000000")</f>
-        <v>001458006</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A109" s="1" t="str">
-        <f>TEXT(A107,"000000000")</f>
-        <v>001458000</v>
       </c>
     </row>
   </sheetData>

--- a/nuevo proyecto.xlsx
+++ b/nuevo proyecto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autopartesymas-my.sharepoint.com/personal/luis_torres_apymsa_com_mx/Documents/Escritorio/APP JOSE LUIS/APP ANDROIDS/Nueva carpeta (4)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F13016D7-1A43-4A0E-AB9E-3C3BE493EEAF}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A1CB225-63F5-46C8-93EA-DA12AC05F136}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{75B1F3C8-71D0-457A-B54E-A3BBFEA49E49}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="246">
   <si>
     <t>Marca</t>
   </si>
@@ -741,6 +741,33 @@
   </si>
   <si>
     <t>https://resources.apymsa.com.mx/imagenes/FotosSpeed/1457500/14575003a.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/6accc5f5b65d030fa0bde4d9d31997e3a4032529/62000%202RS.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/6203%202RS.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/6303%202RS.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/66-82756.wepp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/66-82759.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/B10-50D.JPG</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/B8-85D.wepp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/D411HD.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/D702XHD.wepp</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1205,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1212,7 +1239,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1229,7 +1256,7 @@
         <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -1246,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1263,7 +1290,7 @@
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1280,7 +1307,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1297,7 +1324,7 @@
         <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1314,7 +1341,7 @@
         <v>135</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1331,7 +1358,7 @@
         <v>150</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">

--- a/nuevo proyecto.xlsx
+++ b/nuevo proyecto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autopartesymas-my.sharepoint.com/personal/luis_torres_apymsa_com_mx/Documents/Escritorio/APP JOSE LUIS/APP ANDROIDS/Nueva carpeta (4)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A1CB225-63F5-46C8-93EA-DA12AC05F136}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{CB4B6A4D-B43D-4C0A-9655-2C6835E52C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B0F9B85-7777-41E8-87FB-FA777A2B3A06}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{75B1F3C8-71D0-457A-B54E-A3BBFEA49E49}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="276">
   <si>
     <t>Marca</t>
   </si>
@@ -383,9 +383,6 @@
     <t>005248M2</t>
   </si>
   <si>
-    <t>032029E2</t>
-  </si>
-  <si>
     <t>0249-BALERO ALT. CHEVR CUTLASS=60000ZZ=6000W=6-2000-4W</t>
   </si>
   <si>
@@ -701,36 +698,18 @@
     <t>PUBLICO EN GENERAL</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7f5f183f5d176a341e21ee5fa37f8ee7ad31176a/DIFUS-T4.png</t>
-  </si>
-  <si>
     <t>SERGIO PELGO ARREDONDO</t>
   </si>
   <si>
     <t>EJ.COMPUERTAS</t>
   </si>
   <si>
-    <t>001457500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RELEVADOR UNIVERSAL 24V 30A-40A WEISCHLER </t>
-  </si>
-  <si>
     <t>WEISCHLER</t>
   </si>
   <si>
-    <t xml:space="preserve">RELEVADOR UNIVERSAL 12V 20A-30A FORD CHRYSLER CHEVROLET JEEP BOSCH </t>
-  </si>
-  <si>
     <t>BOSCH</t>
   </si>
   <si>
-    <t>001458006</t>
-  </si>
-  <si>
-    <t>001458000</t>
-  </si>
-  <si>
     <t>RELEVADOR UNIVERSAL 12V 20A-30A FORD CHRYSLER CHEVROLET JEEP WEISCHLER</t>
   </si>
   <si>
@@ -743,41 +722,153 @@
     <t>https://resources.apymsa.com.mx/imagenes/FotosSpeed/1457500/14575003a.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/6accc5f5b65d030fa0bde4d9d31997e3a4032529/62000%202RS.webp</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/6203%202RS.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/6303%202RS.webp</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/66-82756.wepp</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/66-82759.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/B10-50D.JPG</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/B8-85D.wepp</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/D411HD.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/7d07f34cc9c806699ac9c3258fc31a094364d173/D702XHD.wepp</t>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/62000 2RS.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/6202 2RS.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/6203 2RS.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/6303 2RS.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/66-82756.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/66-82759.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/B10-50D.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/B8-85D.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/D411HD.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/D702XHD.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/DIFUS-T1-1.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/DIFUS-T1-2.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/DIFUS-T2-1.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/DIFUS-T2-2.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/DIFUS-T4-1.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/DIFUS-T4-2.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/F784.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/IH738.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/IH782.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/IN220.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/IN221.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/IN224.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/IN439.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/JGO-17.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/JGO-3.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/JGO-4.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/JGO-6.webp</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/JGO-8.webp</t>
+  </si>
+  <si>
+    <t>NASCA</t>
+  </si>
+  <si>
+    <t>HELLA</t>
+  </si>
+  <si>
+    <t>SYLVANIA</t>
+  </si>
+  <si>
+    <t>RELEVADOR UNIVERSAL 12V 20A-30A FORD CHRYSLER CHEVROLET JEEP BOSCH</t>
+  </si>
+  <si>
+    <t>RELEVADOR UNIVERSAL 24V 30A-40A WEISCHLER</t>
+  </si>
+  <si>
+    <t>MOTOR CONDENSADOR 24V COMPLETO TIPO SPAL QBH CARFAN</t>
+  </si>
+  <si>
+    <t>CARFAN</t>
+  </si>
+  <si>
+    <t>https://resources.apymsa.com.mx/imagenes/FotosSpeed/2882914/28829143a.jpg</t>
+  </si>
+  <si>
+    <t>MARCHA DELCO 39MT 12V 11D CAMPANA ROTABLE TOTAL PARTS</t>
+  </si>
+  <si>
+    <t>NPC40190</t>
+  </si>
+  <si>
+    <t>TOTAL PARTS</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/NPC40190.JPG</t>
+  </si>
+  <si>
+    <t>MARCHA AUTOMRIZ BOSCH PLGR CW 12V 3KW 9D KHD</t>
+  </si>
+  <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>https://resources.apymsa.com.mx/imagenes/FotosSpeed/2787110/27871103a.jpg</t>
+  </si>
+  <si>
+    <t>PORTACARBON ISKRA 12V 4 CARBONES</t>
+  </si>
+  <si>
+    <t>KONIGMANN</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JOSELITO198004/cotizador-v1/main/250716.WEBP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -817,6 +908,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -835,27 +934,42 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
     <cellStyle name="Moneda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2CCF5908-B2CF-4903-ABA5-8C9D3E1EA3BE}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1165,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE22E9D8-5D11-4958-B13F-1AFF91466E25}">
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="1"/>
@@ -1196,16 +1310,16 @@
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D2" s="4">
+        <v>220</v>
+      </c>
+      <c r="D2" s="5">
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1213,16 +1327,16 @@
         <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D3" s="4">
+        <v>220</v>
+      </c>
+      <c r="D3" s="5">
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -1230,16 +1344,16 @@
         <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D4" s="4">
+        <v>220</v>
+      </c>
+      <c r="D4" s="5">
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1247,16 +1361,16 @@
         <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D5" s="4">
+        <v>220</v>
+      </c>
+      <c r="D5" s="5">
         <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -1264,16 +1378,16 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D6" s="4">
+        <v>220</v>
+      </c>
+      <c r="D6" s="5">
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1281,16 +1395,16 @@
         <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D7" s="4">
+        <v>220</v>
+      </c>
+      <c r="D7" s="5">
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1298,16 +1412,16 @@
         <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D8" s="4">
+        <v>220</v>
+      </c>
+      <c r="D8" s="5">
         <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1315,16 +1429,16 @@
         <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D9" s="4">
+        <v>220</v>
+      </c>
+      <c r="D9" s="5">
         <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1332,16 +1446,16 @@
         <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="4">
+        <v>220</v>
+      </c>
+      <c r="D10" s="5">
         <v>135</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1349,16 +1463,16 @@
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D11" s="4">
+        <v>220</v>
+      </c>
+      <c r="D11" s="5">
         <v>150</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1366,16 +1480,16 @@
         <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D12" s="4">
+        <v>220</v>
+      </c>
+      <c r="D12" s="5">
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1383,16 +1497,16 @@
         <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D13" s="4">
+        <v>220</v>
+      </c>
+      <c r="D13" s="5">
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1400,16 +1514,16 @@
         <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="4">
+        <v>220</v>
+      </c>
+      <c r="D14" s="5">
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1417,16 +1531,16 @@
         <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D15" s="4">
+        <v>220</v>
+      </c>
+      <c r="D15" s="5">
         <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1434,16 +1548,16 @@
         <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D16" s="4">
+        <v>220</v>
+      </c>
+      <c r="D16" s="5">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1451,16 +1565,16 @@
         <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="4">
+        <v>220</v>
+      </c>
+      <c r="D17" s="5">
         <v>10</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>223</v>
+      <c r="E17" s="4" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1468,16 +1582,16 @@
         <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D18" s="4">
+        <v>220</v>
+      </c>
+      <c r="D18" s="5">
         <v>110</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1485,16 +1599,16 @@
         <v>32</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D19" s="4">
+        <v>220</v>
+      </c>
+      <c r="D19" s="5">
         <v>265</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1502,16 +1616,16 @@
         <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D20" s="4">
+        <v>220</v>
+      </c>
+      <c r="D20" s="5">
         <v>190</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1519,16 +1633,16 @@
         <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D21" s="4">
+        <v>220</v>
+      </c>
+      <c r="D21" s="5">
         <v>220</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1536,16 +1650,16 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D22" s="4">
+        <v>220</v>
+      </c>
+      <c r="D22" s="5">
         <v>200</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -1553,16 +1667,16 @@
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" s="4">
+        <v>220</v>
+      </c>
+      <c r="D23" s="5">
         <v>240</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -1570,16 +1684,16 @@
         <v>37</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D24" s="4">
+        <v>220</v>
+      </c>
+      <c r="D24" s="5">
         <v>240</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -1587,16 +1701,16 @@
         <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D25" s="4">
+        <v>220</v>
+      </c>
+      <c r="D25" s="5">
         <v>25</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -1604,16 +1718,16 @@
         <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D26" s="4">
+        <v>220</v>
+      </c>
+      <c r="D26" s="5">
         <v>28</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -1621,16 +1735,16 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D27" s="4">
+        <v>220</v>
+      </c>
+      <c r="D27" s="5">
         <v>38</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -1638,16 +1752,16 @@
         <v>41</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D28" s="4">
+        <v>220</v>
+      </c>
+      <c r="D28" s="5">
         <v>38</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -1655,16 +1769,16 @@
         <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D29" s="4">
+        <v>220</v>
+      </c>
+      <c r="D29" s="5">
         <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -1672,12 +1786,12 @@
         <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D30" s="4">
+        <v>220</v>
+      </c>
+      <c r="D30" s="5">
         <v>7</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1689,12 +1803,12 @@
         <v>44</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D31" s="4">
+        <v>220</v>
+      </c>
+      <c r="D31" s="5">
         <v>6</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -1706,12 +1820,12 @@
         <v>45</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D32" s="4">
+        <v>220</v>
+      </c>
+      <c r="D32" s="5">
         <v>450</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -1723,12 +1837,12 @@
         <v>46</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D33" s="4">
+        <v>220</v>
+      </c>
+      <c r="D33" s="5">
         <v>90</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -1740,12 +1854,12 @@
         <v>47</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D34" s="4">
+        <v>220</v>
+      </c>
+      <c r="D34" s="5">
         <v>65</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1757,12 +1871,12 @@
         <v>48</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D35" s="4">
+        <v>220</v>
+      </c>
+      <c r="D35" s="5">
         <v>1500</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1774,12 +1888,12 @@
         <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D36" s="4">
+        <v>220</v>
+      </c>
+      <c r="D36" s="5">
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -1791,12 +1905,12 @@
         <v>50</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D37" s="4">
+        <v>220</v>
+      </c>
+      <c r="D37" s="5">
         <v>1.4</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -1808,12 +1922,12 @@
         <v>51</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D38" s="4">
+        <v>220</v>
+      </c>
+      <c r="D38" s="5">
         <v>27</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -1825,12 +1939,12 @@
         <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D39" s="4">
+        <v>220</v>
+      </c>
+      <c r="D39" s="5">
         <v>65</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -1842,12 +1956,12 @@
         <v>53</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D40" s="4">
+        <v>220</v>
+      </c>
+      <c r="D40" s="5">
         <v>70</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -1859,12 +1973,12 @@
         <v>54</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D41" s="4">
+        <v>220</v>
+      </c>
+      <c r="D41" s="5">
         <v>65</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -1876,12 +1990,12 @@
         <v>55</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D42" s="4">
+        <v>220</v>
+      </c>
+      <c r="D42" s="5">
         <v>72</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -1893,12 +2007,12 @@
         <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D43" s="4">
+        <v>220</v>
+      </c>
+      <c r="D43" s="5">
         <v>75</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -1910,12 +2024,12 @@
         <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D44" s="4">
+        <v>220</v>
+      </c>
+      <c r="D44" s="5">
         <v>65</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -1927,12 +2041,12 @@
         <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D45" s="4">
+        <v>220</v>
+      </c>
+      <c r="D45" s="5">
         <v>260</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -1944,12 +2058,12 @@
         <v>59</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D46" s="4">
+        <v>220</v>
+      </c>
+      <c r="D46" s="5">
         <v>250</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -1961,12 +2075,12 @@
         <v>60</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D47" s="4">
+        <v>220</v>
+      </c>
+      <c r="D47" s="5">
         <v>165</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -1978,12 +2092,12 @@
         <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D48" s="4">
+        <v>220</v>
+      </c>
+      <c r="D48" s="5">
         <v>0.85</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -1995,12 +2109,12 @@
         <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D49" s="4">
+        <v>220</v>
+      </c>
+      <c r="D49" s="5">
         <v>1.1000000000000001</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -2012,12 +2126,12 @@
         <v>63</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D50" s="4">
+        <v>220</v>
+      </c>
+      <c r="D50" s="5">
         <v>1500</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -2029,12 +2143,12 @@
         <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D51" s="4">
+        <v>220</v>
+      </c>
+      <c r="D51" s="5">
         <v>1650</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -2046,12 +2160,12 @@
         <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D52" s="4">
+        <v>220</v>
+      </c>
+      <c r="D52" s="5">
         <v>1850</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -2063,12 +2177,12 @@
         <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D53" s="4">
+        <v>220</v>
+      </c>
+      <c r="D53" s="5">
         <v>1450</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -2080,12 +2194,12 @@
         <v>67</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D54" s="4">
+        <v>220</v>
+      </c>
+      <c r="D54" s="5">
         <v>1700</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -2097,12 +2211,12 @@
         <v>68</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D55" s="4">
+        <v>220</v>
+      </c>
+      <c r="D55" s="5">
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -2114,12 +2228,12 @@
         <v>69</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D56" s="4">
+        <v>220</v>
+      </c>
+      <c r="D56" s="5">
         <v>28</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -2131,12 +2245,12 @@
         <v>70</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D57" s="4">
+        <v>220</v>
+      </c>
+      <c r="D57" s="5">
         <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -2148,12 +2262,12 @@
         <v>71</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D58" s="4">
+        <v>220</v>
+      </c>
+      <c r="D58" s="5">
         <v>200</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -2165,12 +2279,12 @@
         <v>72</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D59" s="4">
+        <v>220</v>
+      </c>
+      <c r="D59" s="5">
         <v>3.6</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -2182,12 +2296,12 @@
         <v>73</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D60" s="4">
+        <v>258</v>
+      </c>
+      <c r="D60" s="5">
         <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -2199,12 +2313,12 @@
         <v>74</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D61" s="4">
+        <v>258</v>
+      </c>
+      <c r="D61" s="5">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -2216,12 +2330,12 @@
         <v>75</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D62" s="4">
+        <v>220</v>
+      </c>
+      <c r="D62" s="5">
         <v>280</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -2233,12 +2347,12 @@
         <v>76</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D63" s="4">
+        <v>220</v>
+      </c>
+      <c r="D63" s="5">
         <v>1.5</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -2250,12 +2364,12 @@
         <v>77</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D64" s="4">
+        <v>220</v>
+      </c>
+      <c r="D64" s="5">
         <v>1.7</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -2267,12 +2381,12 @@
         <v>78</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D65" s="4">
+        <v>220</v>
+      </c>
+      <c r="D65" s="5">
         <v>2.2999999999999998</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -2284,12 +2398,12 @@
         <v>79</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D66" s="4">
+        <v>220</v>
+      </c>
+      <c r="D66" s="5">
         <v>65</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -2301,12 +2415,12 @@
         <v>80</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D67" s="4">
+        <v>220</v>
+      </c>
+      <c r="D67" s="5">
         <v>70</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -2318,12 +2432,12 @@
         <v>81</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D68" s="4">
+        <v>220</v>
+      </c>
+      <c r="D68" s="5">
         <v>0.8</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -2335,12 +2449,12 @@
         <v>82</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D69" s="4">
+        <v>220</v>
+      </c>
+      <c r="D69" s="5">
         <v>0.8</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -2352,12 +2466,12 @@
         <v>83</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D70" s="4">
+        <v>220</v>
+      </c>
+      <c r="D70" s="5">
         <v>0.8</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -2369,12 +2483,12 @@
         <v>84</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D71" s="4">
+        <v>220</v>
+      </c>
+      <c r="D71" s="5">
         <v>0.8</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -2386,12 +2500,12 @@
         <v>85</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D72" s="4">
+        <v>220</v>
+      </c>
+      <c r="D72" s="5">
         <v>0.8</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -2403,12 +2517,12 @@
         <v>86</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D73" s="4">
+        <v>220</v>
+      </c>
+      <c r="D73" s="5">
         <v>99</v>
       </c>
       <c r="E73" s="1" t="s">
@@ -2420,12 +2534,12 @@
         <v>87</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D74" s="4">
+        <v>220</v>
+      </c>
+      <c r="D74" s="5">
         <v>0.85</v>
       </c>
       <c r="E74" s="1" t="s">
@@ -2437,12 +2551,12 @@
         <v>88</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D75" s="4">
+        <v>220</v>
+      </c>
+      <c r="D75" s="5">
         <v>0.85</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -2454,12 +2568,12 @@
         <v>89</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D76" s="4">
+        <v>220</v>
+      </c>
+      <c r="D76" s="5">
         <v>0.85</v>
       </c>
       <c r="E76" s="1" t="s">
@@ -2471,12 +2585,12 @@
         <v>90</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D77" s="4">
+        <v>220</v>
+      </c>
+      <c r="D77" s="5">
         <v>0.85</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -2488,12 +2602,12 @@
         <v>91</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D78" s="4">
+        <v>220</v>
+      </c>
+      <c r="D78" s="5">
         <v>0.8</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -2505,12 +2619,12 @@
         <v>92</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D79" s="4">
+        <v>220</v>
+      </c>
+      <c r="D79" s="5">
         <v>0.8</v>
       </c>
       <c r="E79" s="1" t="s">
@@ -2522,12 +2636,12 @@
         <v>93</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D80" s="4">
+        <v>220</v>
+      </c>
+      <c r="D80" s="5">
         <v>0.8</v>
       </c>
       <c r="E80" s="1" t="s">
@@ -2539,12 +2653,12 @@
         <v>94</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D81" s="4">
+        <v>220</v>
+      </c>
+      <c r="D81" s="5">
         <v>0.8</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -2556,12 +2670,12 @@
         <v>95</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D82" s="4">
+        <v>220</v>
+      </c>
+      <c r="D82" s="5">
         <v>0.8</v>
       </c>
       <c r="E82" s="1" t="s">
@@ -2573,12 +2687,12 @@
         <v>96</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D83" s="4">
+        <v>220</v>
+      </c>
+      <c r="D83" s="5">
         <v>330</v>
       </c>
       <c r="E83" s="1" t="s">
@@ -2590,12 +2704,12 @@
         <v>97</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D84" s="4">
+        <v>220</v>
+      </c>
+      <c r="D84" s="5">
         <v>90</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -2607,12 +2721,12 @@
         <v>98</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D85" s="4">
+        <v>220</v>
+      </c>
+      <c r="D85" s="5">
         <v>90</v>
       </c>
       <c r="E85" s="1" t="s">
@@ -2624,12 +2738,12 @@
         <v>99</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D86" s="4">
+        <v>220</v>
+      </c>
+      <c r="D86" s="5">
         <v>120</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -2641,12 +2755,12 @@
         <v>100</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D87" s="4">
+        <v>220</v>
+      </c>
+      <c r="D87" s="5">
         <v>26</v>
       </c>
       <c r="E87" s="1" t="s">
@@ -2658,12 +2772,12 @@
         <v>101</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D88" s="4">
+        <v>259</v>
+      </c>
+      <c r="D88" s="5">
         <v>35</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -2675,12 +2789,12 @@
         <v>102</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D89" s="4">
+        <v>259</v>
+      </c>
+      <c r="D89" s="5">
         <v>50</v>
       </c>
       <c r="E89" s="1" t="s">
@@ -2692,12 +2806,12 @@
         <v>103</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D90" s="4">
+        <v>259</v>
+      </c>
+      <c r="D90" s="5">
         <v>52</v>
       </c>
       <c r="E90" s="1" t="s">
@@ -2709,12 +2823,12 @@
         <v>104</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D91" s="4">
+        <v>259</v>
+      </c>
+      <c r="D91" s="5">
         <v>4</v>
       </c>
       <c r="E91" s="1" t="s">
@@ -2726,12 +2840,12 @@
         <v>105</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D92" s="4">
+        <v>259</v>
+      </c>
+      <c r="D92" s="5">
         <v>4</v>
       </c>
       <c r="E92" s="1" t="s">
@@ -2743,12 +2857,12 @@
         <v>106</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D93" s="4">
+        <v>259</v>
+      </c>
+      <c r="D93" s="5">
         <v>4</v>
       </c>
       <c r="E93" s="1" t="s">
@@ -2760,12 +2874,12 @@
         <v>107</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D94" s="4">
+        <v>259</v>
+      </c>
+      <c r="D94" s="5">
         <v>4</v>
       </c>
       <c r="E94" s="1" t="s">
@@ -2777,12 +2891,12 @@
         <v>108</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D95" s="4">
+        <v>260</v>
+      </c>
+      <c r="D95" s="5">
         <v>185</v>
       </c>
       <c r="E95" s="1" t="s">
@@ -2794,12 +2908,12 @@
         <v>109</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D96" s="4">
+        <v>260</v>
+      </c>
+      <c r="D96" s="5">
         <v>180</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -2811,12 +2925,12 @@
         <v>110</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D97" s="4">
+        <v>260</v>
+      </c>
+      <c r="D97" s="5">
         <v>190</v>
       </c>
       <c r="E97" s="1" t="s">
@@ -2828,12 +2942,12 @@
         <v>111</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D98" s="4">
+        <v>220</v>
+      </c>
+      <c r="D98" s="5">
         <v>123</v>
       </c>
       <c r="E98" s="1" t="s">
@@ -2845,12 +2959,12 @@
         <v>112</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D99" s="4">
+        <v>220</v>
+      </c>
+      <c r="D99" s="5">
         <v>90</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -2862,12 +2976,12 @@
         <v>113</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D100" s="4">
+        <v>220</v>
+      </c>
+      <c r="D100" s="5">
         <v>75</v>
       </c>
       <c r="E100" s="1" t="s">
@@ -2879,12 +2993,12 @@
         <v>114</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D101" s="4">
+        <v>220</v>
+      </c>
+      <c r="D101" s="5">
         <v>60</v>
       </c>
       <c r="E101" s="1" t="s">
@@ -2896,12 +3010,12 @@
         <v>115</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D102" s="4">
+        <v>259</v>
+      </c>
+      <c r="D102" s="5">
         <v>199</v>
       </c>
       <c r="E102" s="1" t="s">
@@ -2913,29 +3027,29 @@
         <v>116</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D103" s="5">
+        <v>499</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" s="6">
+        <v>3200000</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D103" s="4">
-        <v>499</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A104" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C104" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D104" s="4">
+        <v>220</v>
+      </c>
+      <c r="D104" s="5">
         <v>65</v>
       </c>
       <c r="E104" s="1" t="s">
@@ -2943,61 +3057,136 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A105" s="1" t="s">
-        <v>226</v>
+      <c r="A105" s="1">
+        <v>1457500</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D105" s="1">
         <v>75</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
-        <v>231</v>
+      <c r="A106" s="1">
+        <v>1458006</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D106" s="1">
         <v>60</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A107" s="1" t="s">
-        <v>232</v>
+      <c r="A107" s="1">
+        <v>1458000</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D107" s="1">
         <v>50</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" s="1">
+        <v>2882914</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1600</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D109" s="1">
+        <v>4827.58</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" s="1">
+        <v>2787110</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D110" s="1">
+        <v>3103.44</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" s="1">
+        <v>250716</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D111" s="1">
+        <v>200</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E104" xr:uid="{EE22E9D8-5D11-4958-B13F-1AFF91466E25}"/>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="E109" r:id="rId1" xr:uid="{ADA01DEE-4E9F-4CF2-9074-B7C9EE3C2299}"/>
+    <hyperlink ref="E111" r:id="rId2" xr:uid="{36702467-3958-4807-A05F-62559A84D61C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -3040,7 +3229,7 @@
         <v>9999</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
@@ -3060,10 +3249,10 @@
         <v>9998</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D3" s="2">
         <v>6681620106</v>
